--- a/data/Terre di Pedemonte/investment_decision/Cavigliano_MFH_from_2015_investment_decision.xlsx
+++ b/data/Terre di Pedemonte/investment_decision/Cavigliano_MFH_from_2015_investment_decision.xlsx
@@ -461,22 +461,22 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>scen_cp_dr_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_dr_candidate_unit</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>scen_cp_cu_invested_available_unit</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>scen_cp_cu_candidate_unit</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_dr_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_dr_candidate_unit</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -495,7 +495,7 @@
         <v>46023</v>
       </c>
       <c r="B2" t="n">
-        <v>4.029855256403806</v>
+        <v>2.271743461002</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -509,19 +509,19 @@
         <v>460.8705047121257</v>
       </c>
       <c r="F2" t="n">
-        <v>4.322698963565392</v>
+        <v>2.267020626081359</v>
       </c>
       <c r="G2" t="n">
         <v>460.8705047121257</v>
       </c>
       <c r="H2" t="n">
-        <v>4.033047447188019</v>
+        <v>2.269907053044097</v>
       </c>
       <c r="I2" t="n">
         <v>460.8705047121257</v>
       </c>
       <c r="J2" t="n">
-        <v>4.326078095238098</v>
+        <v>2.252219262054468</v>
       </c>
       <c r="K2" t="n">
         <v>460.8705047121257</v>
@@ -532,7 +532,7 @@
         <v>47849</v>
       </c>
       <c r="B3" t="n">
-        <v>4.029855256403806</v>
+        <v>2.271743461002</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -546,19 +546,19 @@
         <v>460.8705047121257</v>
       </c>
       <c r="F3" t="n">
-        <v>4.322698963565392</v>
+        <v>2.267020626081359</v>
       </c>
       <c r="G3" t="n">
         <v>460.8705047121257</v>
       </c>
       <c r="H3" t="n">
-        <v>4.033047447188019</v>
+        <v>2.269907053044097</v>
       </c>
       <c r="I3" t="n">
         <v>460.8705047121257</v>
       </c>
       <c r="J3" t="n">
-        <v>4.326078095238098</v>
+        <v>2.252219262054468</v>
       </c>
       <c r="K3" t="n">
         <v>460.8705047121257</v>
@@ -569,7 +569,7 @@
         <v>49675</v>
       </c>
       <c r="B4" t="n">
-        <v>4.029855256403806</v>
+        <v>2.271743461002</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -583,19 +583,19 @@
         <v>460.8705047121257</v>
       </c>
       <c r="F4" t="n">
-        <v>4.322698963565392</v>
+        <v>2.267020626081359</v>
       </c>
       <c r="G4" t="n">
         <v>460.8705047121257</v>
       </c>
       <c r="H4" t="n">
-        <v>4.033047447188019</v>
+        <v>2.269907053044097</v>
       </c>
       <c r="I4" t="n">
         <v>460.8705047121257</v>
       </c>
       <c r="J4" t="n">
-        <v>4.326078095238098</v>
+        <v>2.252219262054468</v>
       </c>
       <c r="K4" t="n">
         <v>460.8705047121257</v>
@@ -606,7 +606,7 @@
         <v>51502</v>
       </c>
       <c r="B5" t="n">
-        <v>4.029855256403806</v>
+        <v>2.271743461002</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -620,19 +620,19 @@
         <v>460.8705047121257</v>
       </c>
       <c r="F5" t="n">
-        <v>4.322698963565392</v>
+        <v>2.267020626081359</v>
       </c>
       <c r="G5" t="n">
         <v>460.8705047121257</v>
       </c>
       <c r="H5" t="n">
-        <v>4.033047447188019</v>
+        <v>2.269907053044097</v>
       </c>
       <c r="I5" t="n">
         <v>460.8705047121257</v>
       </c>
       <c r="J5" t="n">
-        <v>4.326078095238098</v>
+        <v>2.252219262054468</v>
       </c>
       <c r="K5" t="n">
         <v>460.8705047121257</v>
@@ -643,7 +643,7 @@
         <v>53328</v>
       </c>
       <c r="B6" t="n">
-        <v>4.029855256403805</v>
+        <v>2.283563846507328</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -657,19 +657,19 @@
         <v>460.8705047121257</v>
       </c>
       <c r="F6" t="n">
-        <v>4.322698963565392</v>
+        <v>2.267020626081359</v>
       </c>
       <c r="G6" t="n">
         <v>460.8705047121257</v>
       </c>
       <c r="H6" t="n">
-        <v>4.033047447188019</v>
+        <v>2.269907053044097</v>
       </c>
       <c r="I6" t="n">
         <v>460.8705047121257</v>
       </c>
       <c r="J6" t="n">
-        <v>4.326078095238098</v>
+        <v>2.252219262054468</v>
       </c>
       <c r="K6" t="n">
         <v>460.8705047121257</v>
@@ -684,32 +684,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Cavigliano_b_MFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Cavigliano_b_MFH_from_2015</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6913057570681885</v>
+        <v>1.75311</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6913057570681885</v>
+        <v>1.75311</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6913057570681885</v>
+        <v>1.75311</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6913057570681885</v>
+        <v>1.75311</v>
       </c>
     </row>
     <row r="8">
@@ -721,32 +721,32 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Cavigliano_b_MFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Cavigliano_b_MFH_from_2015</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6913057570681885</v>
+        <v>1.75311</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6913057570681885</v>
+        <v>1.75311</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6913057570681885</v>
+        <v>1.75311</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6913057570681885</v>
+        <v>1.75311</v>
       </c>
     </row>
     <row r="9">
@@ -758,32 +758,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Cavigliano_b_MFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Cavigliano_b_MFH_from_2015</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6913057570681885</v>
+        <v>1.75311</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6913057570681885</v>
+        <v>1.75311</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6913057570681885</v>
+        <v>1.75311</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6913057570681885</v>
+        <v>1.75311</v>
       </c>
     </row>
     <row r="10">
@@ -795,32 +795,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Cavigliano_b_MFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Cavigliano_b_MFH_from_2015</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6913057570681885</v>
+        <v>1.75311</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6913057570681885</v>
+        <v>1.75311</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6913057570681885</v>
+        <v>1.75311</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6913057570681885</v>
+        <v>1.75311</v>
       </c>
     </row>
     <row r="11">
@@ -832,32 +832,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Cavigliano_b_MFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Cavigliano_b_MFH_from_2015</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E11" t="n">
-        <v>0.6913057570681885</v>
+        <v>1.75311</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6913057570681885</v>
+        <v>1.75311</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6913057570681885</v>
+        <v>1.75311</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6913057570681885</v>
+        <v>1.75311</v>
       </c>
     </row>
     <row r="12">
@@ -865,7 +865,7 @@
         <v>46023</v>
       </c>
       <c r="B12" t="n">
-        <v>0.0003687345388235294</v>
+        <v>0.0002611521189791995</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -879,19 +879,19 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0003687345388235294</v>
+        <v>0.00027254292</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0003687345388235294</v>
+        <v>0.0002595155863444575</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0003687345388235294</v>
+        <v>0.00027254292</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
@@ -902,7 +902,7 @@
         <v>47849</v>
       </c>
       <c r="B13" t="n">
-        <v>0.0003687345388234509</v>
+        <v>0.0002611521189791995</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -916,19 +916,19 @@
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0003687345388235294</v>
+        <v>0.00027254292</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0003687345388235294</v>
+        <v>0.0002595155863444575</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0003687345388235294</v>
+        <v>0.00027254292</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -939,7 +939,7 @@
         <v>49675</v>
       </c>
       <c r="B14" t="n">
-        <v>0.0003687345388235295</v>
+        <v>0.0002611521189791995</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -953,19 +953,19 @@
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0003687345388235294</v>
+        <v>0.00027254292</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0003687345388235294</v>
+        <v>0.0002595155863444575</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0003687345388235294</v>
+        <v>0.00027254292</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
@@ -976,7 +976,7 @@
         <v>51502</v>
       </c>
       <c r="B15" t="n">
-        <v>0.0003687345388235294</v>
+        <v>0.0002725429199999959</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -990,19 +990,19 @@
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0003687345388235294</v>
+        <v>0.00027254292</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0003687345388235294</v>
+        <v>0.000259515586344459</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0003687345388235294</v>
+        <v>0.00027254292</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -1013,7 +1013,7 @@
         <v>53328</v>
       </c>
       <c r="B16" t="n">
-        <v>0.0003687345388235294</v>
+        <v>0.00027254292</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1027,19 +1027,19 @@
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0003687345388235294</v>
+        <v>0.00027254292</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0003687345388235294</v>
+        <v>0.0002595155863444575</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0003687345388235294</v>
+        <v>0.00027254292</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
@@ -1050,7 +1050,7 @@
         <v>46023</v>
       </c>
       <c r="B17" t="n">
-        <v>0.02248311552577822</v>
+        <v>0.005447090257830059</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1064,19 +1064,19 @@
         <v>0.05723401319999999</v>
       </c>
       <c r="F17" t="n">
-        <v>0.02248311552577822</v>
+        <v>0.005605858928154103</v>
       </c>
       <c r="G17" t="n">
         <v>0.05723401319999999</v>
       </c>
       <c r="H17" t="n">
-        <v>0.02248311552577822</v>
+        <v>0.005273208665389086</v>
       </c>
       <c r="I17" t="n">
         <v>0.05723401319999999</v>
       </c>
       <c r="J17" t="n">
-        <v>0.02248311552577822</v>
+        <v>0.005547615264534633</v>
       </c>
       <c r="K17" t="n">
         <v>0.05723401319999999</v>
@@ -1087,7 +1087,7 @@
         <v>47849</v>
       </c>
       <c r="B18" t="n">
-        <v>0.0442882245</v>
+        <v>0.02604401939153994</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1101,19 +1101,19 @@
         <v>0.05723401319999999</v>
       </c>
       <c r="F18" t="n">
-        <v>0.04283064561349473</v>
+        <v>0.02602667495872685</v>
       </c>
       <c r="G18" t="n">
         <v>0.05723401319999999</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0442882245</v>
+        <v>0.02528455129368973</v>
       </c>
       <c r="I18" t="n">
         <v>0.05723401319999999</v>
       </c>
       <c r="J18" t="n">
-        <v>0.04274673804674441</v>
+        <v>0.02512262876307483</v>
       </c>
       <c r="K18" t="n">
         <v>0.05723401319999999</v>
@@ -1124,7 +1124,7 @@
         <v>49675</v>
       </c>
       <c r="B19" t="n">
-        <v>0.0442882245</v>
+        <v>0.02604401939153995</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1138,19 +1138,19 @@
         <v>0.05723401319999999</v>
       </c>
       <c r="F19" t="n">
-        <v>0.04283064561349473</v>
+        <v>0.02602667495872685</v>
       </c>
       <c r="G19" t="n">
         <v>0.05723401319999999</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0442882245</v>
+        <v>0.02528455129368973</v>
       </c>
       <c r="I19" t="n">
         <v>0.05723401319999999</v>
       </c>
       <c r="J19" t="n">
-        <v>0.04274673804674441</v>
+        <v>0.02512262876307483</v>
       </c>
       <c r="K19" t="n">
         <v>0.05723401319999999</v>
@@ -1161,7 +1161,7 @@
         <v>51502</v>
       </c>
       <c r="B20" t="n">
-        <v>0.0442882245</v>
+        <v>0.02555089875000001</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1175,19 +1175,19 @@
         <v>0.05723401319999999</v>
       </c>
       <c r="F20" t="n">
-        <v>0.04188812258291126</v>
+        <v>0.02555089875</v>
       </c>
       <c r="G20" t="n">
         <v>0.05723401319999999</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0442882245</v>
+        <v>0.0238475055</v>
       </c>
       <c r="I20" t="n">
         <v>0.05723401319999999</v>
       </c>
       <c r="J20" t="n">
-        <v>0.04205474630736076</v>
+        <v>0.0238475055</v>
       </c>
       <c r="K20" t="n">
         <v>0.05723401319999999</v>
@@ -1198,7 +1198,7 @@
         <v>53328</v>
       </c>
       <c r="B21" t="n">
-        <v>0.02248311552577822</v>
+        <v>0.005812094802692641</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1212,19 +1212,19 @@
         <v>0.05723401319999999</v>
       </c>
       <c r="F21" t="n">
-        <v>0.02154059249519475</v>
+        <v>0.005877757390597759</v>
       </c>
       <c r="G21" t="n">
         <v>0.05723401319999999</v>
       </c>
       <c r="H21" t="n">
-        <v>0.02248311552577822</v>
+        <v>0.003836162871699356</v>
       </c>
       <c r="I21" t="n">
         <v>0.05723401319999999</v>
       </c>
       <c r="J21" t="n">
-        <v>0.02179112378639456</v>
+        <v>0.004272492001459811</v>
       </c>
       <c r="K21" t="n">
         <v>0.05723401319999999</v>
@@ -1420,7 +1420,7 @@
         <v>46023</v>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>0.01824420510846006</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1434,19 +1434,19 @@
         <v>0.05723401319999999</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>0.01808543643813601</v>
       </c>
       <c r="G27" t="n">
         <v>0.05723401319999999</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>0.01841808670090103</v>
       </c>
       <c r="I27" t="n">
         <v>0.05723401319999999</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>0.01814368010175548</v>
       </c>
       <c r="K27" t="n">
         <v>0.05723401319999999</v>
@@ -1457,7 +1457,7 @@
         <v>47849</v>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>0.01824420510846006</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1471,19 +1471,19 @@
         <v>0.05723401319999999</v>
       </c>
       <c r="F28" t="n">
-        <v>0.001457578886505279</v>
+        <v>0.01826154954127315</v>
       </c>
       <c r="G28" t="n">
         <v>0.05723401319999999</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>0.01900367320631205</v>
       </c>
       <c r="I28" t="n">
         <v>0.05723401319999999</v>
       </c>
       <c r="J28" t="n">
-        <v>0.001541486453255588</v>
+        <v>0.01916559573692517</v>
       </c>
       <c r="K28" t="n">
         <v>0.05723401319999999</v>
@@ -1494,7 +1494,7 @@
         <v>49675</v>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>0.01824420510846006</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1508,19 +1508,19 @@
         <v>0.05723401319999999</v>
       </c>
       <c r="F29" t="n">
-        <v>0.001457578886505279</v>
+        <v>0.01826154954127315</v>
       </c>
       <c r="G29" t="n">
         <v>0.05723401319999999</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>0.01981927257801028</v>
       </c>
       <c r="I29" t="n">
         <v>0.05723401319999999</v>
       </c>
       <c r="J29" t="n">
-        <v>0.001541486453255588</v>
+        <v>0.01987937649356991</v>
       </c>
       <c r="K29" t="n">
         <v>0.05723401319999999</v>
@@ -1531,7 +1531,7 @@
         <v>51502</v>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>0.01873732575</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1545,19 +1545,19 @@
         <v>0.05723401319999999</v>
       </c>
       <c r="F30" t="n">
-        <v>0.002400101917088744</v>
+        <v>0.01873732575</v>
       </c>
       <c r="G30" t="n">
         <v>0.05723401319999999</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>0.020440719</v>
       </c>
       <c r="I30" t="n">
         <v>0.05723401319999999</v>
       </c>
       <c r="J30" t="n">
-        <v>0.002233478192639241</v>
+        <v>0.020440719</v>
       </c>
       <c r="K30" t="n">
         <v>0.05723401319999999</v>
@@ -1568,7 +1568,7 @@
         <v>53328</v>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>0.01873732575</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1582,19 +1582,19 @@
         <v>0.05723401319999999</v>
       </c>
       <c r="F31" t="n">
-        <v>0.0009425230305834646</v>
+        <v>0.01873732575</v>
       </c>
       <c r="G31" t="n">
         <v>0.05723401319999999</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>0.02031899865920523</v>
       </c>
       <c r="I31" t="n">
         <v>0.05723401319999999</v>
       </c>
       <c r="J31" t="n">
-        <v>0.0006919917393836535</v>
+        <v>0.02004706872117018</v>
       </c>
       <c r="K31" t="n">
         <v>0.05723401319999999</v>
@@ -2160,7 +2160,7 @@
         <v>46023</v>
       </c>
       <c r="B47" t="n">
-        <v>0.03423067093145459</v>
+        <v>0.02942802198325612</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -2174,19 +2174,19 @@
         <v>0.1509639670417728</v>
       </c>
       <c r="F47" t="n">
-        <v>0.03445135646787839</v>
+        <v>0.03132762259313536</v>
       </c>
       <c r="G47" t="n">
         <v>0.1509639670417728</v>
       </c>
       <c r="H47" t="n">
-        <v>0.03873376242959085</v>
+        <v>0.02946014292166714</v>
       </c>
       <c r="I47" t="n">
         <v>0.1509639670417728</v>
       </c>
       <c r="J47" t="n">
-        <v>0.03859257166354324</v>
+        <v>0.03136882671457412</v>
       </c>
       <c r="K47" t="n">
         <v>0.1509639670417728</v>
@@ -2197,7 +2197,7 @@
         <v>47849</v>
       </c>
       <c r="B48" t="n">
-        <v>0.03423067093145459</v>
+        <v>0.02942802198325612</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -2211,19 +2211,19 @@
         <v>0.1509639670417728</v>
       </c>
       <c r="F48" t="n">
-        <v>0.03445135646787839</v>
+        <v>0.03132762259313536</v>
       </c>
       <c r="G48" t="n">
         <v>0.1509639670417728</v>
       </c>
       <c r="H48" t="n">
-        <v>0.03873376242959085</v>
+        <v>0.02946014292166714</v>
       </c>
       <c r="I48" t="n">
         <v>0.1509639670417728</v>
       </c>
       <c r="J48" t="n">
-        <v>0.03859257166354324</v>
+        <v>0.03136882671457412</v>
       </c>
       <c r="K48" t="n">
         <v>0.1509639670417728</v>
@@ -2234,7 +2234,7 @@
         <v>49675</v>
       </c>
       <c r="B49" t="n">
-        <v>0.03423067093145459</v>
+        <v>0.02942802198325612</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -2248,19 +2248,19 @@
         <v>0.1509639670417728</v>
       </c>
       <c r="F49" t="n">
-        <v>0.03445135646787839</v>
+        <v>0.03132762259313536</v>
       </c>
       <c r="G49" t="n">
         <v>0.1509639670417728</v>
       </c>
       <c r="H49" t="n">
-        <v>0.03873376242959085</v>
+        <v>0.02946014292166714</v>
       </c>
       <c r="I49" t="n">
         <v>0.1509639670417728</v>
       </c>
       <c r="J49" t="n">
-        <v>0.03859257166354324</v>
+        <v>0.03136882671457412</v>
       </c>
       <c r="K49" t="n">
         <v>0.1509639670417728</v>
@@ -2345,7 +2345,7 @@
         <v>46023</v>
       </c>
       <c r="B52" t="n">
-        <v>0.02132876946576158</v>
+        <v>0.02429421051266508</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -2359,19 +2359,19 @@
         <v>0.1509639670417728</v>
       </c>
       <c r="F52" t="n">
-        <v>0.02009578040817716</v>
+        <v>0.02249738670339312</v>
       </c>
       <c r="G52" t="n">
         <v>0.1509639670417728</v>
       </c>
       <c r="H52" t="n">
-        <v>0.01869507570727853</v>
+        <v>0.02256479950728471</v>
       </c>
       <c r="I52" t="n">
         <v>0.1509639670417728</v>
       </c>
       <c r="J52" t="n">
-        <v>0.01832178348520047</v>
+        <v>0.02068411817181306</v>
       </c>
       <c r="K52" t="n">
         <v>0.1509639670417728</v>
@@ -2382,7 +2382,7 @@
         <v>47849</v>
       </c>
       <c r="B53" t="n">
-        <v>0.02132876946576158</v>
+        <v>0.02429421051266508</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -2396,19 +2396,19 @@
         <v>0.1509639670417728</v>
       </c>
       <c r="F53" t="n">
-        <v>0.02009578040817716</v>
+        <v>0.02249738670339312</v>
       </c>
       <c r="G53" t="n">
         <v>0.1509639670417728</v>
       </c>
       <c r="H53" t="n">
-        <v>0.01869507570727853</v>
+        <v>0.02256479950728471</v>
       </c>
       <c r="I53" t="n">
         <v>0.1509639670417728</v>
       </c>
       <c r="J53" t="n">
-        <v>0.01832178348520047</v>
+        <v>0.02068411817181306</v>
       </c>
       <c r="K53" t="n">
         <v>0.1509639670417728</v>
@@ -2419,7 +2419,7 @@
         <v>49675</v>
       </c>
       <c r="B54" t="n">
-        <v>0.02132876946576158</v>
+        <v>0.02429421051266508</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2433,19 +2433,19 @@
         <v>0.1509639670417728</v>
       </c>
       <c r="F54" t="n">
-        <v>0.02009578040817716</v>
+        <v>0.02249738670339312</v>
       </c>
       <c r="G54" t="n">
         <v>0.1509639670417728</v>
       </c>
       <c r="H54" t="n">
-        <v>0.01869507570727853</v>
+        <v>0.02256479950728471</v>
       </c>
       <c r="I54" t="n">
         <v>0.1509639670417728</v>
       </c>
       <c r="J54" t="n">
-        <v>0.01832178348520047</v>
+        <v>0.02068411817181306</v>
       </c>
       <c r="K54" t="n">
         <v>0.1509639670417728</v>
@@ -2456,7 +2456,7 @@
         <v>51502</v>
       </c>
       <c r="B55" t="n">
-        <v>0.02976725769823641</v>
+        <v>0.03189822443572045</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2470,19 +2470,19 @@
         <v>0.1509639670417728</v>
       </c>
       <c r="F55" t="n">
-        <v>0.02997276077811395</v>
+        <v>0.02829805395807147</v>
       </c>
       <c r="G55" t="n">
         <v>0.1509639670417728</v>
       </c>
       <c r="H55" t="n">
-        <v>0.02701220597201769</v>
+        <v>0.0320061670988404</v>
       </c>
       <c r="I55" t="n">
         <v>0.1509639670417728</v>
       </c>
       <c r="J55" t="n">
-        <v>0.02702490121674506</v>
+        <v>0.02744015065919629</v>
       </c>
       <c r="K55" t="n">
         <v>0.1509639670417728</v>
@@ -2493,7 +2493,7 @@
         <v>53328</v>
       </c>
       <c r="B56" t="n">
-        <v>0.02976725769823641</v>
+        <v>0.03189822443572045</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2507,19 +2507,19 @@
         <v>0.1509639670417728</v>
       </c>
       <c r="F56" t="n">
-        <v>0.02997276077811395</v>
+        <v>0.02829805395807147</v>
       </c>
       <c r="G56" t="n">
         <v>0.1509639670417728</v>
       </c>
       <c r="H56" t="n">
-        <v>0.02701220597201769</v>
+        <v>0.0320061670988404</v>
       </c>
       <c r="I56" t="n">
         <v>0.1509639670417728</v>
       </c>
       <c r="J56" t="n">
-        <v>0.02702490121674506</v>
+        <v>0.02744015065919629</v>
       </c>
       <c r="K56" t="n">
         <v>0.1509639670417728</v>
@@ -2715,7 +2715,7 @@
         <v>46023</v>
       </c>
       <c r="B62" t="n">
-        <v>0.01606344708169674</v>
+        <v>0.009086092707704552</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -2729,19 +2729,19 @@
         <v>0.1509639670417728</v>
       </c>
       <c r="F62" t="n">
-        <v>0.01465669582929833</v>
+        <v>0.009405695797497752</v>
       </c>
       <c r="G62" t="n">
         <v>0.1509639670417728</v>
       </c>
       <c r="H62" t="n">
-        <v>0.01549163344428815</v>
+        <v>0.009058261212232932</v>
       </c>
       <c r="I62" t="n">
         <v>0.1509639670417728</v>
       </c>
       <c r="J62" t="n">
-        <v>0.01440562721701157</v>
+        <v>0.009512140477027394</v>
       </c>
       <c r="K62" t="n">
         <v>0.1509639670417728</v>
@@ -2752,7 +2752,7 @@
         <v>47849</v>
       </c>
       <c r="B63" t="n">
-        <v>0.01606344708169674</v>
+        <v>0.009086092707704552</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -2766,19 +2766,19 @@
         <v>0.1509639670417728</v>
       </c>
       <c r="F63" t="n">
-        <v>0.01465669582929833</v>
+        <v>0.009405695797497752</v>
       </c>
       <c r="G63" t="n">
         <v>0.1509639670417728</v>
       </c>
       <c r="H63" t="n">
-        <v>0.01549163344428815</v>
+        <v>0.009058261212232932</v>
       </c>
       <c r="I63" t="n">
         <v>0.1509639670417728</v>
       </c>
       <c r="J63" t="n">
-        <v>0.01440562721701157</v>
+        <v>0.009512140477027394</v>
       </c>
       <c r="K63" t="n">
         <v>0.1509639670417728</v>
@@ -2789,7 +2789,7 @@
         <v>49675</v>
       </c>
       <c r="B64" t="n">
-        <v>0.01606344708169674</v>
+        <v>0.009086092707704552</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2803,19 +2803,19 @@
         <v>0.1509639670417728</v>
       </c>
       <c r="F64" t="n">
-        <v>0.01465669582929833</v>
+        <v>0.009405695797497752</v>
       </c>
       <c r="G64" t="n">
         <v>0.1509639670417728</v>
       </c>
       <c r="H64" t="n">
-        <v>0.01549163344428815</v>
+        <v>0.009058261212232932</v>
       </c>
       <c r="I64" t="n">
         <v>0.1509639670417728</v>
       </c>
       <c r="J64" t="n">
-        <v>0.01440562721701157</v>
+        <v>0.009512140477027394</v>
       </c>
       <c r="K64" t="n">
         <v>0.1509639670417728</v>
@@ -2826,7 +2826,7 @@
         <v>51502</v>
       </c>
       <c r="B65" t="n">
-        <v>0.03025122959851159</v>
+        <v>0.01582164173503822</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -2840,19 +2840,19 @@
         <v>0.1509639670417728</v>
       </c>
       <c r="F65" t="n">
-        <v>0.02867302164131412</v>
+        <v>0.01953131233789125</v>
       </c>
       <c r="G65" t="n">
         <v>0.1509639670417728</v>
       </c>
       <c r="H65" t="n">
-        <v>0.03299131793042932</v>
+        <v>0.01572622231987622</v>
       </c>
       <c r="I65" t="n">
         <v>0.1509639670417728</v>
       </c>
       <c r="J65" t="n">
-        <v>0.03160504152296721</v>
+        <v>0.02042567063133665</v>
       </c>
       <c r="K65" t="n">
         <v>0.1509639670417728</v>
@@ -2863,7 +2863,7 @@
         <v>53328</v>
       </c>
       <c r="B66" t="n">
-        <v>0.03025122959851159</v>
+        <v>0.01582164173503822</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -2877,19 +2877,19 @@
         <v>0.1509639670417728</v>
       </c>
       <c r="F66" t="n">
-        <v>0.02867302164131412</v>
+        <v>0.01953131233789125</v>
       </c>
       <c r="G66" t="n">
         <v>0.1509639670417728</v>
       </c>
       <c r="H66" t="n">
-        <v>0.03299131793042932</v>
+        <v>0.01572622231987622</v>
       </c>
       <c r="I66" t="n">
         <v>0.1509639670417728</v>
       </c>
       <c r="J66" t="n">
-        <v>0.03160504152296721</v>
+        <v>0.02042567063133665</v>
       </c>
       <c r="K66" t="n">
         <v>0.1509639670417728</v>
@@ -3270,7 +3270,7 @@
         <v>46023</v>
       </c>
       <c r="B77" t="n">
-        <v>0.02259455675286453</v>
+        <v>0.02137659293228438</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -3284,19 +3284,19 @@
         <v>0.1509639670417728</v>
       </c>
       <c r="F77" t="n">
-        <v>0.02364090664910362</v>
+        <v>0.02086206821924957</v>
       </c>
       <c r="G77" t="n">
         <v>0.1509639670417728</v>
       </c>
       <c r="H77" t="n">
-        <v>0.02128200925631893</v>
+        <v>0.02313303940930288</v>
       </c>
       <c r="I77" t="n">
         <v>0.1509639670417728</v>
       </c>
       <c r="J77" t="n">
-        <v>0.02150891730898641</v>
+        <v>0.02263413262939087</v>
       </c>
       <c r="K77" t="n">
         <v>0.1509639670417728</v>
@@ -3307,7 +3307,7 @@
         <v>47849</v>
       </c>
       <c r="B78" t="n">
-        <v>0.02259455675286453</v>
+        <v>0.02137659293228438</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -3321,19 +3321,19 @@
         <v>0.1509639670417728</v>
       </c>
       <c r="F78" t="n">
-        <v>0.02364090664910362</v>
+        <v>0.02086206821924957</v>
       </c>
       <c r="G78" t="n">
         <v>0.1509639670417728</v>
       </c>
       <c r="H78" t="n">
-        <v>0.02128200925631893</v>
+        <v>0.02313303940930288</v>
       </c>
       <c r="I78" t="n">
         <v>0.1509639670417728</v>
       </c>
       <c r="J78" t="n">
-        <v>0.02150891730898641</v>
+        <v>0.02263413262939087</v>
       </c>
       <c r="K78" t="n">
         <v>0.1509639670417728</v>
@@ -3344,7 +3344,7 @@
         <v>49675</v>
       </c>
       <c r="B79" t="n">
-        <v>0.02259455675286453</v>
+        <v>0.02137659293228438</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -3358,19 +3358,19 @@
         <v>0.1509639670417728</v>
       </c>
       <c r="F79" t="n">
-        <v>0.02364090664910362</v>
+        <v>0.02086206821924957</v>
       </c>
       <c r="G79" t="n">
         <v>0.1509639670417728</v>
       </c>
       <c r="H79" t="n">
-        <v>0.02128200925631893</v>
+        <v>0.02313303940930288</v>
       </c>
       <c r="I79" t="n">
         <v>0.1509639670417728</v>
       </c>
       <c r="J79" t="n">
-        <v>0.02150891730898641</v>
+        <v>0.02263413262939087</v>
       </c>
       <c r="K79" t="n">
         <v>0.1509639670417728</v>
